--- a/result.xlsx
+++ b/result.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-6.7B_128_1024_32" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-6.7B_128_1024_64" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-6.7B_128_1024_128" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-2.7B_1024_128_128" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-2.7B_1024_128_32" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-2.7B_1024_128_64" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,4 +937,517 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>244608</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2609152</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2609152</v>
+      </c>
+      <c r="E2" t="n">
+        <v>81536</v>
+      </c>
+      <c r="F2" t="n">
+        <v>81536</v>
+      </c>
+      <c r="G2" t="n">
+        <v>81536</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5707520</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1002433536</v>
+      </c>
+      <c r="C3" t="n">
+        <v>334144512</v>
+      </c>
+      <c r="D3" t="n">
+        <v>334144512</v>
+      </c>
+      <c r="E3" t="n">
+        <v>334144512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>334144512</v>
+      </c>
+      <c r="G3" t="n">
+        <v>334144512</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2673156096</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>31309824</v>
+      </c>
+      <c r="C4" t="n">
+        <v>83492864</v>
+      </c>
+      <c r="D4" t="n">
+        <v>83492864</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10436608</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10436608</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10436608</v>
+      </c>
+      <c r="H4" t="n">
+        <v>596738048</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27.45593322717039</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>128311492608</v>
+      </c>
+      <c r="C5" t="n">
+        <v>342163980288</v>
+      </c>
+      <c r="D5" t="n">
+        <v>342163980288</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42770497536</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42770497536</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42770497536</v>
+      </c>
+      <c r="H5" t="n">
+        <v>940950945792</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3226560</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24541184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14448640</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1913216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3235264</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3986144</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51351008</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6039567360</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1457038848</v>
+      </c>
+      <c r="D3" t="n">
+        <v>848845824</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3640762368</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6056864256</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7509626880</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25552705536</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60014592</v>
+      </c>
+      <c r="C4" t="n">
+        <v>39228288</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35573376</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12926976</v>
+      </c>
+      <c r="F4" t="n">
+        <v>41746432</v>
+      </c>
+      <c r="G4" t="n">
+        <v>36880384</v>
+      </c>
+      <c r="H4" t="n">
+        <v>379593216</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.79049842661045</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>114742591488</v>
+      </c>
+      <c r="C5" t="n">
+        <v>182596374528</v>
+      </c>
+      <c r="D5" t="n">
+        <v>139484110848</v>
+      </c>
+      <c r="E5" t="n">
+        <v>46018854912</v>
+      </c>
+      <c r="F5" t="n">
+        <v>116734820352</v>
+      </c>
+      <c r="G5" t="n">
+        <v>123076214784</v>
+      </c>
+      <c r="H5" t="n">
+        <v>722652966912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3226560</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24541184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14448640</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1913216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3235264</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3986144</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51351008</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6039567360</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1457038848</v>
+      </c>
+      <c r="D3" t="n">
+        <v>848845824</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3640762368</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6056864256</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7509626880</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25552705536</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>53428224</v>
+      </c>
+      <c r="C4" t="n">
+        <v>72288256</v>
+      </c>
+      <c r="D4" t="n">
+        <v>71237632</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17809408</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17809408</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17809408</v>
+      </c>
+      <c r="H4" t="n">
+        <v>474908672</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17.24963236721018</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>209450041344</v>
+      </c>
+      <c r="C5" t="n">
+        <v>291147346329.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>279266721792</v>
+      </c>
+      <c r="E5" t="n">
+        <v>69816680448</v>
+      </c>
+      <c r="F5" t="n">
+        <v>69816680448</v>
+      </c>
+      <c r="G5" t="n">
+        <v>69816680448</v>
+      </c>
+      <c r="H5" t="n">
+        <v>989314150809.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result.xlsx
+++ b/result.xlsx
@@ -1,131 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-6.7B_128_1024_32" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-6.7B_128_1024_64" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPT-6.7B_128_1024_128" sheetId="4" state="visible" r:id="rId4"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -423,6 +295,1032 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>82974720</v>
+      </c>
+      <c r="C2" t="n">
+        <v>878592</v>
+      </c>
+      <c r="D2" t="n">
+        <v>878592</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29655040</v>
+      </c>
+      <c r="F2" t="n">
+        <v>111581184</v>
+      </c>
+      <c r="G2" t="n">
+        <v>114034688</v>
+      </c>
+      <c r="H2" t="n">
+        <v>573793689.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>138864623616</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1863843840</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1863843840</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62898634752</v>
+      </c>
+      <c r="F3" t="n">
+        <v>186475216896</v>
+      </c>
+      <c r="G3" t="n">
+        <v>202346889216</v>
+      </c>
+      <c r="H3" t="n">
+        <v>594313052160</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1076330496</v>
+      </c>
+      <c r="C4" t="n">
+        <v>355520384</v>
+      </c>
+      <c r="D4" t="n">
+        <v>408906112</v>
+      </c>
+      <c r="E4" t="n">
+        <v>295174144</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1291845632</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1189347328</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7179634124.799904</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18.25608348860715</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1710706655232</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1688022465331.201</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1848202562764.805</v>
+      </c>
+      <c r="E5" t="n">
+        <v>722007490560</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2339707551744</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2468567580672</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10777214306304.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>126723840</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15338240</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9030400</v>
+      </c>
+      <c r="E2" t="n">
+        <v>76474240</v>
+      </c>
+      <c r="F2" t="n">
+        <v>127105280</v>
+      </c>
+      <c r="G2" t="n">
+        <v>159594880</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1355874560</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>236868526080</v>
+      </c>
+      <c r="C3" t="n">
+        <v>29140776960</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16976916480</v>
+      </c>
+      <c r="E3" t="n">
+        <v>145586104320</v>
+      </c>
+      <c r="F3" t="n">
+        <v>237526179840</v>
+      </c>
+      <c r="G3" t="n">
+        <v>300697927680</v>
+      </c>
+      <c r="H3" t="n">
+        <v>966796431360</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>63283200</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24517680</v>
+      </c>
+      <c r="D4" t="n">
+        <v>26853040</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14243840</v>
+      </c>
+      <c r="F4" t="n">
+        <v>47390720</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43550720</v>
+      </c>
+      <c r="H4" t="n">
+        <v>529768160</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.731683987954277</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>222416732160</v>
+      </c>
+      <c r="C5" t="n">
+        <v>114122734080</v>
+      </c>
+      <c r="D5" t="n">
+        <v>119531037696</v>
+      </c>
+      <c r="E5" t="n">
+        <v>65689681920</v>
+      </c>
+      <c r="F5" t="n">
+        <v>186429603840</v>
+      </c>
+      <c r="G5" t="n">
+        <v>199619051520</v>
+      </c>
+      <c r="H5" t="n">
+        <v>907808841216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>253447680</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30676480</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18060800</v>
+      </c>
+      <c r="E2" t="n">
+        <v>152948480</v>
+      </c>
+      <c r="F2" t="n">
+        <v>254210560</v>
+      </c>
+      <c r="G2" t="n">
+        <v>319189760</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2710149120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>473737052160</v>
+      </c>
+      <c r="C3" t="n">
+        <v>58281553920</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33953832960</v>
+      </c>
+      <c r="E3" t="n">
+        <v>291172208640</v>
+      </c>
+      <c r="F3" t="n">
+        <v>475052359680</v>
+      </c>
+      <c r="G3" t="n">
+        <v>601395855360</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1933592862720</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>126566400</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49035360</v>
+      </c>
+      <c r="D4" t="n">
+        <v>53706080</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28487680</v>
+      </c>
+      <c r="F4" t="n">
+        <v>94781440</v>
+      </c>
+      <c r="G4" t="n">
+        <v>87101440</v>
+      </c>
+      <c r="H4" t="n">
+        <v>854736320</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.584242307615991</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>293673369600</v>
+      </c>
+      <c r="C5" t="n">
+        <v>228245468160</v>
+      </c>
+      <c r="D5" t="n">
+        <v>239062075392</v>
+      </c>
+      <c r="E5" t="n">
+        <v>117874360320</v>
+      </c>
+      <c r="F5" t="n">
+        <v>293189222400</v>
+      </c>
+      <c r="G5" t="n">
+        <v>310688563200</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1482733059072</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>506895360</v>
+      </c>
+      <c r="C2" t="n">
+        <v>61352960</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36121600</v>
+      </c>
+      <c r="E2" t="n">
+        <v>305896960</v>
+      </c>
+      <c r="F2" t="n">
+        <v>508421120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>638379520</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5418698240</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>947474104320</v>
+      </c>
+      <c r="C3" t="n">
+        <v>116563107840</v>
+      </c>
+      <c r="D3" t="n">
+        <v>67907665920</v>
+      </c>
+      <c r="E3" t="n">
+        <v>582344417280</v>
+      </c>
+      <c r="F3" t="n">
+        <v>950104719360</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1202791710720</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3867185725440</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>212720640</v>
+      </c>
+      <c r="C4" t="n">
+        <v>98070720</v>
+      </c>
+      <c r="D4" t="n">
+        <v>107412160</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56975360</v>
+      </c>
+      <c r="F4" t="n">
+        <v>189562880</v>
+      </c>
+      <c r="G4" t="n">
+        <v>174202880</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1464260480</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.189265997263</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>337874780160</v>
+      </c>
+      <c r="C5" t="n">
+        <v>456490936320</v>
+      </c>
+      <c r="D5" t="n">
+        <v>478124150783.9999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>142293073920</v>
+      </c>
+      <c r="F5" t="n">
+        <v>341332131840</v>
+      </c>
+      <c r="G5" t="n">
+        <v>368762142720</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2124877215744</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>32588160</v>
+      </c>
+      <c r="C2" t="n">
+        <v>274560</v>
+      </c>
+      <c r="D2" t="n">
+        <v>274560</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11630080</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32818560</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33641600</v>
+      </c>
+      <c r="H2" t="n">
+        <v>216036480</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>54416977920</v>
+      </c>
+      <c r="C3" t="n">
+        <v>582451200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>582451200</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24656855040</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54782976000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>61007339520</v>
+      </c>
+      <c r="H3" t="n">
+        <v>196029050880</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>506265600</v>
+      </c>
+      <c r="C4" t="n">
+        <v>111100120</v>
+      </c>
+      <c r="D4" t="n">
+        <v>127783160</v>
+      </c>
+      <c r="E4" t="n">
+        <v>113950720</v>
+      </c>
+      <c r="F4" t="n">
+        <v>379125760</v>
+      </c>
+      <c r="G4" t="n">
+        <v>348405760</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4058894800</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.073133602772852</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1779333857280</v>
+      </c>
+      <c r="C5" t="n">
+        <v>527507020416</v>
+      </c>
+      <c r="D5" t="n">
+        <v>577563300864</v>
+      </c>
+      <c r="E5" t="n">
+        <v>525517455360</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1491436830720</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1596952412160</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6498310876800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>65176320</v>
+      </c>
+      <c r="C2" t="n">
+        <v>549120</v>
+      </c>
+      <c r="D2" t="n">
+        <v>549120</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23260160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>65637120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>67283200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>430472960</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>108833955840</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1164902400</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1164902400</v>
+      </c>
+      <c r="E3" t="n">
+        <v>49313710080</v>
+      </c>
+      <c r="F3" t="n">
+        <v>109565952000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>122014679040</v>
+      </c>
+      <c r="H3" t="n">
+        <v>392058101760</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1012531200</v>
+      </c>
+      <c r="C4" t="n">
+        <v>222200240</v>
+      </c>
+      <c r="D4" t="n">
+        <v>255566320</v>
+      </c>
+      <c r="E4" t="n">
+        <v>227901440</v>
+      </c>
+      <c r="F4" t="n">
+        <v>758251520</v>
+      </c>
+      <c r="G4" t="n">
+        <v>696811520</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6479389600</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.11453301094906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2349386956800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1055014040832</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1155126601728</v>
+      </c>
+      <c r="E5" t="n">
+        <v>942994882560</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2345513779200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2485508505600</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10333544766720</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -481,7 +1379,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1296480</v>
+        <v>25955328</v>
       </c>
       <c r="C2" t="n">
         <v>439296</v>
@@ -490,16 +1388,16 @@
         <v>439296</v>
       </c>
       <c r="E2" t="n">
-        <v>463360</v>
+        <v>9306112</v>
       </c>
       <c r="F2" t="n">
-        <v>1743456</v>
+        <v>26150912</v>
       </c>
       <c r="G2" t="n">
-        <v>1781792</v>
+        <v>26780672</v>
       </c>
       <c r="H2" t="n">
-        <v>6163680</v>
+        <v>162817024</v>
       </c>
     </row>
     <row r="3">
@@ -509,25 +1407,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2169759744</v>
+        <v>43818319872</v>
       </c>
       <c r="C3" t="n">
-        <v>29122560</v>
+        <v>931921920</v>
       </c>
       <c r="D3" t="n">
-        <v>29122560</v>
+        <v>931921920</v>
       </c>
       <c r="E3" t="n">
-        <v>982791168</v>
+        <v>19726270464</v>
       </c>
       <c r="F3" t="n">
-        <v>2913675264</v>
+        <v>43928518656</v>
       </c>
       <c r="G3" t="n">
-        <v>3161670144</v>
+        <v>48568025088</v>
       </c>
       <c r="H3" t="n">
-        <v>9286141440</v>
+        <v>157904977920</v>
       </c>
     </row>
     <row r="4">
@@ -537,28 +1435,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>324796416</v>
+        <v>480116736</v>
       </c>
       <c r="C4" t="n">
-        <v>88880096</v>
+        <v>177760192</v>
       </c>
       <c r="D4" t="n">
-        <v>102226528</v>
+        <v>166574848</v>
       </c>
       <c r="E4" t="n">
-        <v>73793536</v>
+        <v>103415808</v>
       </c>
       <c r="F4" t="n">
-        <v>322961408</v>
+        <v>333971456</v>
       </c>
       <c r="G4" t="n">
-        <v>297336832</v>
+        <v>295043072</v>
       </c>
       <c r="H4" t="n">
-        <v>2321695091.199973</v>
+        <v>2818056896</v>
       </c>
       <c r="I4" t="n">
-        <v>14.11382576644196</v>
+        <v>11.62787026994078</v>
       </c>
     </row>
     <row r="5">
@@ -568,25 +1466,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1139838183014.4</v>
+        <v>917940731904</v>
       </c>
       <c r="C5" t="n">
-        <v>422005616332.8002</v>
+        <v>844011232665.6003</v>
       </c>
       <c r="D5" t="n">
-        <v>462050640691.2012</v>
+        <v>667062730752</v>
       </c>
       <c r="E5" t="n">
-        <v>337315155148.8</v>
+        <v>368150839296</v>
       </c>
       <c r="F5" t="n">
-        <v>1394603143987.2</v>
+        <v>933878562816</v>
       </c>
       <c r="G5" t="n">
-        <v>1371299590963.2</v>
+        <v>984609718272</v>
       </c>
       <c r="H5" t="n">
-        <v>5127112330137.602</v>
+        <v>4715653815705.601</v>
       </c>
     </row>
   </sheetData>
@@ -652,25 +1550,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1296480</v>
+        <v>51910656</v>
       </c>
       <c r="C2" t="n">
-        <v>439296</v>
+        <v>878592</v>
       </c>
       <c r="D2" t="n">
-        <v>439296</v>
+        <v>878592</v>
       </c>
       <c r="E2" t="n">
-        <v>463360</v>
+        <v>18612224</v>
       </c>
       <c r="F2" t="n">
-        <v>1743456</v>
+        <v>52301824</v>
       </c>
       <c r="G2" t="n">
-        <v>1781792</v>
+        <v>53561344</v>
       </c>
       <c r="H2" t="n">
-        <v>6163680</v>
+        <v>324994048</v>
       </c>
     </row>
     <row r="3">
@@ -680,25 +1578,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2169759744</v>
+        <v>87636639744</v>
       </c>
       <c r="C3" t="n">
-        <v>29122560</v>
+        <v>1863843840</v>
       </c>
       <c r="D3" t="n">
-        <v>29122560</v>
+        <v>1863843840</v>
       </c>
       <c r="E3" t="n">
-        <v>982791168</v>
+        <v>39452540928</v>
       </c>
       <c r="F3" t="n">
-        <v>2913675264</v>
+        <v>87857037312</v>
       </c>
       <c r="G3" t="n">
-        <v>3161670144</v>
+        <v>97136050176</v>
       </c>
       <c r="H3" t="n">
-        <v>9286141440</v>
+        <v>315809955840</v>
       </c>
     </row>
     <row r="4">
@@ -708,28 +1606,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>649592832</v>
+        <v>661684224</v>
       </c>
       <c r="C4" t="n">
-        <v>177760192</v>
+        <v>355520384</v>
       </c>
       <c r="D4" t="n">
-        <v>204453056</v>
+        <v>333149696</v>
       </c>
       <c r="E4" t="n">
-        <v>147587072</v>
+        <v>206831616</v>
       </c>
       <c r="F4" t="n">
-        <v>645922816</v>
+        <v>667942912</v>
       </c>
       <c r="G4" t="n">
-        <v>594673664</v>
+        <v>590086144</v>
       </c>
       <c r="H4" t="n">
-        <v>3988030182.399941</v>
+        <v>4682204544</v>
       </c>
       <c r="I4" t="n">
-        <v>16.43317552841622</v>
+        <v>13.99682550903953</v>
       </c>
     </row>
     <row r="5">
@@ -739,25 +1637,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1480316682240</v>
+        <v>1056181321728</v>
       </c>
       <c r="C5" t="n">
-        <v>844011232665.6003</v>
+        <v>1688022465331.201</v>
       </c>
       <c r="D5" t="n">
-        <v>924101281382.4025</v>
+        <v>1334125461504</v>
       </c>
       <c r="E5" t="n">
-        <v>596555857920</v>
+        <v>447070863360</v>
       </c>
       <c r="F5" t="n">
-        <v>2010065141760</v>
+        <v>1098774478848</v>
       </c>
       <c r="G5" t="n">
-        <v>2091000004608</v>
+        <v>1179441954816</v>
       </c>
       <c r="H5" t="n">
-        <v>7946050200576.003</v>
+        <v>6803616545587.201</v>
       </c>
     </row>
   </sheetData>
@@ -823,7 +1721,862 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1296480</v>
+        <v>103821312</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1757184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1757184</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37224448</v>
+      </c>
+      <c r="F2" t="n">
+        <v>104603648</v>
+      </c>
+      <c r="G2" t="n">
+        <v>107122688</v>
+      </c>
+      <c r="H2" t="n">
+        <v>649348096</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>175273279488</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3727687680</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3727687680</v>
+      </c>
+      <c r="E3" t="n">
+        <v>78905081856</v>
+      </c>
+      <c r="F3" t="n">
+        <v>175714074624</v>
+      </c>
+      <c r="G3" t="n">
+        <v>194272100352</v>
+      </c>
+      <c r="H3" t="n">
+        <v>631619911680</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>830570496</v>
+      </c>
+      <c r="C4" t="n">
+        <v>711040768</v>
+      </c>
+      <c r="D4" t="n">
+        <v>666299392</v>
+      </c>
+      <c r="E4" t="n">
+        <v>297795584</v>
+      </c>
+      <c r="F4" t="n">
+        <v>836829184</v>
+      </c>
+      <c r="G4" t="n">
+        <v>856981504</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7278136064</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18.00900654335445</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1402186235904</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3376044930662.401</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2668250923008</v>
+      </c>
+      <c r="E5" t="n">
+        <v>631240654848</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1405712596992</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1554176802816</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11037612144230.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>81576960</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12270592</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7224320</v>
+      </c>
+      <c r="E2" t="n">
+        <v>48919040</v>
+      </c>
+      <c r="F2" t="n">
+        <v>109061120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>128270848</v>
+      </c>
+      <c r="H2" t="n">
+        <v>872614707.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>152521555968</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23312621568</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13581533184</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93161447424</v>
+      </c>
+      <c r="F3" t="n">
+        <v>203901886464</v>
+      </c>
+      <c r="G3" t="n">
+        <v>241699332096</v>
+      </c>
+      <c r="H3" t="n">
+        <v>728178376704</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>40599552</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19614144</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21482432</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9224192</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40370176</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37167104</v>
+      </c>
+      <c r="H4" t="n">
+        <v>311122918.4000007</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13.16521463948826</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>142479772876.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>91298187264</v>
+      </c>
+      <c r="D5" t="n">
+        <v>95624830156.79977</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42164394393.60001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>174325392998.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>171412448870.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>717305026559.9999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>163153920</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24541184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14448640</v>
+      </c>
+      <c r="E2" t="n">
+        <v>97838080</v>
+      </c>
+      <c r="F2" t="n">
+        <v>218122240</v>
+      </c>
+      <c r="G2" t="n">
+        <v>256541696</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1744589414.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>305043111936</v>
+      </c>
+      <c r="C3" t="n">
+        <v>46625243136</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27163066368</v>
+      </c>
+      <c r="E3" t="n">
+        <v>186322894848</v>
+      </c>
+      <c r="F3" t="n">
+        <v>407803772928</v>
+      </c>
+      <c r="G3" t="n">
+        <v>483398664192</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1456356753408</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>81199104</v>
+      </c>
+      <c r="C4" t="n">
+        <v>39228288</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42964864</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18448384</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80740352</v>
+      </c>
+      <c r="G4" t="n">
+        <v>74334208</v>
+      </c>
+      <c r="H4" t="n">
+        <v>540325836.8000005</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15.16122206651435</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>185039585280</v>
+      </c>
+      <c r="C5" t="n">
+        <v>182596374528</v>
+      </c>
+      <c r="D5" t="n">
+        <v>191249660313.5995</v>
+      </c>
+      <c r="E5" t="n">
+        <v>74569482240</v>
+      </c>
+      <c r="F5" t="n">
+        <v>251258142720</v>
+      </c>
+      <c r="G5" t="n">
+        <v>261375000576</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1146088245657.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>326307840</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49082368</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28897280</v>
+      </c>
+      <c r="E2" t="n">
+        <v>195676160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>436244480</v>
+      </c>
+      <c r="G2" t="n">
+        <v>513083392</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3488538828.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>610086223872</v>
+      </c>
+      <c r="C3" t="n">
+        <v>93250486272</v>
+      </c>
+      <c r="D3" t="n">
+        <v>54326132736</v>
+      </c>
+      <c r="E3" t="n">
+        <v>372645789696</v>
+      </c>
+      <c r="F3" t="n">
+        <v>815607545856</v>
+      </c>
+      <c r="G3" t="n">
+        <v>966797328384</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2912713506816</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>134541312</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78456576</v>
+      </c>
+      <c r="D4" t="n">
+        <v>85929728</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36896768</v>
+      </c>
+      <c r="F4" t="n">
+        <v>161480704</v>
+      </c>
+      <c r="G4" t="n">
+        <v>148668416</v>
+      </c>
+      <c r="H4" t="n">
+        <v>970874777.5999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.87550277132671</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>213838331904</v>
+      </c>
+      <c r="C5" t="n">
+        <v>365192749056</v>
+      </c>
+      <c r="D5" t="n">
+        <v>382499320627.1991</v>
+      </c>
+      <c r="E5" t="n">
+        <v>90250936320</v>
+      </c>
+      <c r="F5" t="n">
+        <v>292463443968</v>
+      </c>
+      <c r="G5" t="n">
+        <v>308570947584</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1652815729459.199</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20743680</v>
+      </c>
+      <c r="C2" t="n">
+        <v>219648</v>
+      </c>
+      <c r="D2" t="n">
+        <v>219648</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7413760</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27895296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28508672</v>
+      </c>
+      <c r="H2" t="n">
+        <v>143928422.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prompt energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>34716155904</v>
+      </c>
+      <c r="C3" t="n">
+        <v>465960960</v>
+      </c>
+      <c r="D3" t="n">
+        <v>465960960</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15724658688</v>
+      </c>
+      <c r="F3" t="n">
+        <v>46618804224</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50586722304</v>
+      </c>
+      <c r="H3" t="n">
+        <v>148578263040</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decoder runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>324796416</v>
+      </c>
+      <c r="C4" t="n">
+        <v>88880096</v>
+      </c>
+      <c r="D4" t="n">
+        <v>102226528</v>
+      </c>
+      <c r="E4" t="n">
+        <v>73793536</v>
+      </c>
+      <c r="F4" t="n">
+        <v>322961408</v>
+      </c>
+      <c r="G4" t="n">
+        <v>297336832</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2342142323.199973</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13.99061008181195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decode energy (pJ)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1139838183014.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>422005616332.8002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>462050640691.2012</v>
+      </c>
+      <c r="E5" t="n">
+        <v>337315155148.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1394603143987.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1371299590963.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5127112330137.602</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>createQKV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>throughput (K tokens/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt runtime (ns)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>41487360</v>
       </c>
       <c r="C2" t="n">
         <v>439296</v>
@@ -832,16 +2585,16 @@
         <v>439296</v>
       </c>
       <c r="E2" t="n">
-        <v>463360</v>
+        <v>14827520</v>
       </c>
       <c r="F2" t="n">
-        <v>1743456</v>
+        <v>55790592</v>
       </c>
       <c r="G2" t="n">
-        <v>1781792</v>
+        <v>57017344</v>
       </c>
       <c r="H2" t="n">
-        <v>6163680</v>
+        <v>287216844.8</v>
       </c>
     </row>
     <row r="3">
@@ -851,25 +2604,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2169759744</v>
+        <v>69432311808</v>
       </c>
       <c r="C3" t="n">
-        <v>29122560</v>
+        <v>931921920</v>
       </c>
       <c r="D3" t="n">
-        <v>29122560</v>
+        <v>931921920</v>
       </c>
       <c r="E3" t="n">
-        <v>982791168</v>
+        <v>31449317376</v>
       </c>
       <c r="F3" t="n">
-        <v>2913675264</v>
+        <v>93237608448</v>
       </c>
       <c r="G3" t="n">
-        <v>3161670144</v>
+        <v>101173444608</v>
       </c>
       <c r="H3" t="n">
-        <v>9286141440</v>
+        <v>297156526080</v>
       </c>
     </row>
     <row r="4">
@@ -879,28 +2632,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1076330496</v>
+        <v>649592832</v>
       </c>
       <c r="C4" t="n">
-        <v>355520384</v>
+        <v>177760192</v>
       </c>
       <c r="D4" t="n">
-        <v>408906112</v>
+        <v>204453056</v>
       </c>
       <c r="E4" t="n">
-        <v>295174144</v>
+        <v>147587072</v>
       </c>
       <c r="F4" t="n">
-        <v>1291845632</v>
+        <v>645922816</v>
       </c>
       <c r="G4" t="n">
-        <v>1189347328</v>
+        <v>594673664</v>
       </c>
       <c r="H4" t="n">
-        <v>7097845196.799904</v>
+        <v>4028924646.399941</v>
       </c>
       <c r="I4" t="n">
-        <v>18.46644951612842</v>
+        <v>16.26637521219462</v>
       </c>
     </row>
     <row r="5">
@@ -910,25 +2663,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1710706655232</v>
+        <v>1480316682240</v>
       </c>
       <c r="C5" t="n">
-        <v>1688022465331.201</v>
+        <v>844011232665.6003</v>
       </c>
       <c r="D5" t="n">
-        <v>1848202562764.805</v>
+        <v>924101281382.4025</v>
       </c>
       <c r="E5" t="n">
-        <v>722007490560</v>
+        <v>596555857920</v>
       </c>
       <c r="F5" t="n">
-        <v>2339707551744</v>
+        <v>2010065141760</v>
       </c>
       <c r="G5" t="n">
-        <v>2468567580672</v>
+        <v>2091000004608</v>
       </c>
       <c r="H5" t="n">
-        <v>10777214306304.01</v>
+        <v>7946050200576.003</v>
       </c>
     </row>
   </sheetData>
